--- a/data/trans_camb/IP24_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP24_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 1,13</t>
+          <t>-14,22; 1,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 7,22</t>
+          <t>-10,66; 7,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,34; -2,55</t>
+          <t>-17,11; -2,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,48; -0,79</t>
+          <t>-15,74; -0,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,34; -2,26</t>
+          <t>-16,98; -2,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 15,65</t>
+          <t>-11,88; 17,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,0; -1,91</t>
+          <t>-12,94; -1,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 0,14</t>
+          <t>-11,97; -0,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 5,46</t>
+          <t>-12,87; 5,7</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-51,65; 6,62</t>
+          <t>-50,45; 6,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,29; 36,17</t>
+          <t>-36,71; 33,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-62,69; -10,89</t>
+          <t>-59,98; -13,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,77; -3,09</t>
+          <t>-56,47; -2,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,56; -10,66</t>
+          <t>-62,35; -14,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,11; 80,19</t>
+          <t>-49,12; 103,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,58; -8,56</t>
+          <t>-48,2; -7,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,71; 0,69</t>
+          <t>-44,07; -0,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-47,95; 26,23</t>
+          <t>-49,7; 27,25</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 1,01</t>
+          <t>-12,84; 0,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,58; -0,3</t>
+          <t>-13,36; -0,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 3,36</t>
+          <t>-13,88; 2,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,45; -1,08</t>
+          <t>-13,63; -1,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 3,22</t>
+          <t>-10,72; 2,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,16; -1,03</t>
+          <t>-13,2; -0,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,47; -2,28</t>
+          <t>-10,87; -2,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,84; -0,93</t>
+          <t>-9,91; -0,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,29; -2,52</t>
+          <t>-12,35; -1,61</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,71; 6,51</t>
+          <t>-41,64; 1,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-42,46; -1,17</t>
+          <t>-42,01; -1,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-46,27; 14,67</t>
+          <t>-46,26; 13,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-49,85; -3,5</t>
+          <t>-50,44; -6,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,27; 16,52</t>
+          <t>-39,1; 9,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,19; -5,52</t>
+          <t>-48,77; -0,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-41,03; -9,46</t>
+          <t>-39,62; -9,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,9; -3,55</t>
+          <t>-36,1; -4,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,25; -10,24</t>
+          <t>-44,27; -6,75</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 6,59</t>
+          <t>-8,31; 6,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 5,78</t>
+          <t>-7,17; 7,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 40,31</t>
+          <t>-2,09; 35,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 5,47</t>
+          <t>-8,88; 5,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 2,66</t>
+          <t>-11,29; 2,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 10,75</t>
+          <t>-4,73; 10,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 3,63</t>
+          <t>-6,62; 4,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 2,16</t>
+          <t>-8,06; 1,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 23,59</t>
+          <t>0,11; 24,16</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,85; 36,9</t>
+          <t>-31,37; 34,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,27; 31,42</t>
+          <t>-28,37; 38,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 214,12</t>
+          <t>-9,57; 184,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-38,98; 36,59</t>
+          <t>-38,76; 32,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,04; 16,0</t>
+          <t>-48,2; 16,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-22,28; 69,18</t>
+          <t>-21,47; 64,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,26; 20,05</t>
+          <t>-27,94; 21,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,01; 11,75</t>
+          <t>-33,59; 10,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 116,08</t>
+          <t>-0,4; 119,99</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 1,47</t>
+          <t>-12,4; 1,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 4,88</t>
+          <t>-9,14; 5,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 1,56</t>
+          <t>-13,91; 1,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-17,79; -5,36</t>
+          <t>-17,98; -5,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,42; -2,57</t>
+          <t>-15,41; -3,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,98; -6,78</t>
+          <t>-19,81; -6,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-12,77; -3,35</t>
+          <t>-13,21; -3,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,87; -1,09</t>
+          <t>-10,83; -1,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,36; -4,56</t>
+          <t>-14,46; -4,73</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-43,66; 8,17</t>
+          <t>-43,07; 8,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-33,02; 22,69</t>
+          <t>-33,2; 24,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-47,07; 7,09</t>
+          <t>-47,52; 7,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-60,05; -22,55</t>
+          <t>-60,18; -22,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-52,18; -10,15</t>
+          <t>-52,91; -13,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,7; -29,1</t>
+          <t>-66,2; -28,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-45,77; -14,8</t>
+          <t>-48,25; -16,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-38,99; -4,88</t>
+          <t>-38,46; -4,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,65; -19,03</t>
+          <t>-51,78; -19,64</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,28; -1,05</t>
+          <t>-9,12; -1,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 0,31</t>
+          <t>-6,98; 0,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 9,66</t>
+          <t>-7,25; 9,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,07; -4,36</t>
+          <t>-10,8; -4,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,96; -3,37</t>
+          <t>-9,94; -3,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,11; -0,8</t>
+          <t>-9,1; -1,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,88; -3,79</t>
+          <t>-8,7; -3,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,45; -2,43</t>
+          <t>-7,51; -2,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 1,32</t>
+          <t>-7,09; 1,64</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-30,25; -4,38</t>
+          <t>-33,24; -6,87</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 1,27</t>
+          <t>-25,87; 0,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-25,93; 38,39</t>
+          <t>-27,24; 40,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,41; -19,22</t>
+          <t>-43,37; -19,05</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,55; -15,81</t>
+          <t>-39,48; -14,66</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,35; -2,86</t>
+          <t>-36,66; -3,81</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-34,85; -16,41</t>
+          <t>-33,7; -16,19</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-29,16; -10,78</t>
+          <t>-29,17; -10,86</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-27,43; 5,63</t>
+          <t>-28,18; 7,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP24_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP24_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 1,3</t>
+          <t>-15,53; 1,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 7,23</t>
+          <t>-10,39; 7,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,11; -2,58</t>
+          <t>-17,57; -2,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,74; -0,98</t>
+          <t>-14,5; -0,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,98; -2,86</t>
+          <t>-16,17; -1,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 17,66</t>
+          <t>-11,89; 17,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,94; -1,74</t>
+          <t>-12,87; -1,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,97; -0,14</t>
+          <t>-11,12; 0,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 5,7</t>
+          <t>-12,4; 6,03</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-50,45; 6,89</t>
+          <t>-52,97; 7,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 33,74</t>
+          <t>-36,5; 34,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-59,98; -13,04</t>
+          <t>-60,92; -9,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-56,47; -2,89</t>
+          <t>-54,28; -0,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,35; -14,79</t>
+          <t>-60,86; -8,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,12; 103,47</t>
+          <t>-48,39; 82,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-48,2; -7,98</t>
+          <t>-48,75; -7,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,07; -0,61</t>
+          <t>-41,69; 1,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-49,7; 27,25</t>
+          <t>-47,97; 31,09</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 0,27</t>
+          <t>-13,48; 0,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,36; -0,62</t>
+          <t>-13,72; 0,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 2,9</t>
+          <t>-14,32; 2,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,63; -1,69</t>
+          <t>-13,46; -1,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 2,07</t>
+          <t>-10,52; 2,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,2; -0,95</t>
+          <t>-13,79; -1,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,87; -2,2</t>
+          <t>-10,92; -1,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,91; -0,94</t>
+          <t>-9,45; -0,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,35; -1,61</t>
+          <t>-11,62; -1,32</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,64; 1,01</t>
+          <t>-42,19; 2,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-42,01; -1,98</t>
+          <t>-43,35; 1,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-46,26; 13,82</t>
+          <t>-46,82; 12,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,44; -6,85</t>
+          <t>-51,24; -8,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,1; 9,96</t>
+          <t>-38,22; 11,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,77; -0,98</t>
+          <t>-50,73; -4,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,62; -9,58</t>
+          <t>-40,23; -8,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,1; -4,59</t>
+          <t>-34,08; -0,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,27; -6,75</t>
+          <t>-41,93; -5,77</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 6,44</t>
+          <t>-9,13; 6,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 7,23</t>
+          <t>-8,25; 5,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 35,55</t>
+          <t>-1,48; 42,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 5,37</t>
+          <t>-8,63; 5,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 2,54</t>
+          <t>-10,63; 2,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 10,44</t>
+          <t>-4,34; 10,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 4,07</t>
+          <t>-6,74; 3,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 1,92</t>
+          <t>-7,88; 2,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 24,16</t>
+          <t>-0,07; 23,25</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,37; 34,2</t>
+          <t>-32,67; 34,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,37; 38,22</t>
+          <t>-31,74; 30,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 184,03</t>
+          <t>-7,46; 210,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-38,76; 32,07</t>
+          <t>-37,88; 33,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,2; 16,1</t>
+          <t>-46,1; 16,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,47; 64,9</t>
+          <t>-19,96; 61,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,94; 21,78</t>
+          <t>-27,45; 20,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 10,11</t>
+          <t>-33,22; 11,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 119,99</t>
+          <t>-0,78; 119,86</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 1,56</t>
+          <t>-12,36; 1,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 5,09</t>
+          <t>-9,49; 4,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 1,29</t>
+          <t>-12,95; 2,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-17,98; -5,3</t>
+          <t>-17,28; -4,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,41; -3,09</t>
+          <t>-15,41; -3,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,81; -6,67</t>
+          <t>-19,64; -6,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,21; -3,75</t>
+          <t>-13,25; -3,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,83; -1,13</t>
+          <t>-10,73; -0,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,46; -4,73</t>
+          <t>-14,46; -4,64</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-43,07; 8,41</t>
+          <t>-43,57; 7,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-33,2; 24,23</t>
+          <t>-32,94; 22,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-47,52; 7,27</t>
+          <t>-46,87; 10,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-60,18; -22,28</t>
+          <t>-58,33; -19,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-52,91; -13,31</t>
+          <t>-52,24; -12,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,2; -28,06</t>
+          <t>-65,54; -27,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-48,25; -16,63</t>
+          <t>-47,54; -16,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-38,46; -4,25</t>
+          <t>-38,35; -3,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,78; -19,64</t>
+          <t>-53,43; -19,57</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,12; -1,51</t>
+          <t>-9,05; -1,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 0,18</t>
+          <t>-7,13; 0,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 9,15</t>
+          <t>-7,26; 9,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,8; -4,13</t>
+          <t>-10,97; -3,99</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,94; -3,15</t>
+          <t>-9,93; -3,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,1; -1,0</t>
+          <t>-9,11; -1,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,7; -3,77</t>
+          <t>-8,75; -3,63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,51; -2,51</t>
+          <t>-7,37; -2,57</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 1,64</t>
+          <t>-7,29; 1,3</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-33,24; -6,87</t>
+          <t>-32,4; -7,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 0,61</t>
+          <t>-26,49; 1,72</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 40,97</t>
+          <t>-27,22; 36,41</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,37; -19,05</t>
+          <t>-43,18; -18,03</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,48; -14,66</t>
+          <t>-39,49; -15,01</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,66; -3,81</t>
+          <t>-36,26; -3,39</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-33,7; -16,19</t>
+          <t>-34,43; -16,05</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-29,17; -10,86</t>
+          <t>-29,05; -11,03</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-28,18; 7,27</t>
+          <t>-28,68; 6,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP24_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP24_R-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-7,7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-9,07</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-3,59</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-7,03</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-1,9</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-10,43</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-7,7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-9,07</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,43</t>
+          <t>-11,92</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-6,11</t>
+          <t>-7,64</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,53; 1,44</t>
+          <t>-15,48; -0,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 7,17</t>
+          <t>-17,34; -2,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,57; -2,1</t>
+          <t>-13,24; 12,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,5; -0,22</t>
+          <t>-15,52; 1,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,17; -1,64</t>
+          <t>-11,16; 7,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 17,14</t>
+          <t>-19,79; -4,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,87; -1,44</t>
+          <t>-13,0; -1,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 0,29</t>
+          <t>-11,08; 0,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 6,03</t>
+          <t>-13,56; 2,02</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-33,37%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-39,33%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-15,58%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-27,93%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-7,53%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-41,41%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-33,37%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-39,33%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-10,53%</t>
+          <t>-47,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-25,37%</t>
+          <t>-31,76%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-52,97; 7,88</t>
+          <t>-57,77; -3,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,5; 34,11</t>
+          <t>-62,56; -10,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-60,92; -9,7</t>
+          <t>-53,46; 65,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-54,28; -0,91</t>
+          <t>-51,65; 6,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,86; -8,98</t>
+          <t>-37,29; 36,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,39; 82,78</t>
+          <t>-65,49; -17,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-48,75; -7,09</t>
+          <t>-47,58; -8,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,69; 1,41</t>
+          <t>-41,71; 0,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-47,97; 31,09</t>
+          <t>-52,08; 11,9</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-7,58</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-4,06</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-9,63</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-6,1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-6,62</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-6,74</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-7,58</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-4,06</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-7,11</t>
+          <t>-10,94</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-7,17</t>
+          <t>-10,38</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 0,6</t>
+          <t>-13,45; -1,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 0,55</t>
+          <t>-9,65; 3,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 2,97</t>
+          <t>-15,4; -3,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,46; -1,79</t>
+          <t>-12,89; 1,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 2,29</t>
+          <t>-13,58; -0,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,79; -1,21</t>
+          <t>-17,96; -4,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,92; -1,95</t>
+          <t>-11,47; -2,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,45; -0,24</t>
+          <t>-9,84; -0,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,62; -1,32</t>
+          <t>-15,05; -6,37</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-32,36%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-17,32%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-41,13%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-21,96%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-23,84%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-24,29%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-32,36%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-17,32%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-30,35%</t>
+          <t>-39,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-28,12%</t>
+          <t>-40,7%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,19; 2,69</t>
+          <t>-49,85; -3,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-43,35; 1,37</t>
+          <t>-36,27; 16,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-46,82; 12,71</t>
+          <t>-57,87; -19,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,24; -8,52</t>
+          <t>-41,71; 6,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,22; 11,63</t>
+          <t>-42,46; -1,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,73; -4,33</t>
+          <t>-57,24; -17,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,23; -8,85</t>
+          <t>-41,03; -9,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,08; -0,97</t>
+          <t>-35,9; -3,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-41,93; -5,77</t>
+          <t>-53,59; -27,52</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,85</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-4,54</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,24</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-0,79</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,03</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12,34</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,85</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,54</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,85</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,77</t>
+          <t>0,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 6,59</t>
+          <t>-8,76; 5,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 5,73</t>
+          <t>-10,87; 2,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 42,19</t>
+          <t>-6,61; 8,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 5,18</t>
+          <t>-8,25; 6,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 2,53</t>
+          <t>-8,95; 5,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 10,48</t>
+          <t>-7,35; 8,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 3,82</t>
+          <t>-6,6; 3,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 2,08</t>
+          <t>-7,93; 2,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 23,25</t>
+          <t>-4,89; 6,92</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-9,34%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-22,95%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-3,49%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-4,56%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>54,39%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-9,34%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-22,95%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 34,43</t>
+          <t>-38,98; 36,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,74; 30,19</t>
+          <t>-47,04; 16,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 210,84</t>
+          <t>-28,89; 56,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,88; 33,79</t>
+          <t>-30,85; 36,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,1; 16,28</t>
+          <t>-32,27; 31,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,96; 61,52</t>
+          <t>-28,5; 44,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,45; 20,65</t>
+          <t>-27,26; 20,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,22; 11,15</t>
+          <t>-33,01; 11,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 119,86</t>
+          <t>-20,26; 37,47</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-11,43</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-9,01</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-12,47</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-5,5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-2,63</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-5,78</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-11,43</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-9,01</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-13,12</t>
+          <t>-7,29</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-9,56</t>
+          <t>-9,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 1,41</t>
+          <t>-17,79; -5,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 4,25</t>
+          <t>-15,42; -2,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 2,06</t>
+          <t>-18,74; -5,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-17,28; -4,68</t>
+          <t>-12,64; 1,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,41; -3,6</t>
+          <t>-9,03; 4,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,64; -6,69</t>
+          <t>-14,49; -0,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,25; -3,89</t>
+          <t>-12,77; -3,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,73; -0,75</t>
+          <t>-10,87; -1,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,46; -4,64</t>
+          <t>-14,72; -5,01</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-43,47%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-34,28%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-47,43%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-22,2%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-10,6%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-23,33%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-43,47%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-34,28%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-49,89%</t>
+          <t>-29,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-37,47%</t>
+          <t>-38,75%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-43,57; 7,54</t>
+          <t>-60,05; -22,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,94; 22,12</t>
+          <t>-52,18; -10,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-46,87; 10,08</t>
+          <t>-63,15; -25,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-58,33; -19,65</t>
+          <t>-43,66; 8,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-52,24; -12,95</t>
+          <t>-33,02; 22,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,54; -27,68</t>
+          <t>-50,72; -1,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-47,54; -16,98</t>
+          <t>-45,77; -14,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-38,35; -3,36</t>
+          <t>-38,99; -4,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,43; -19,57</t>
+          <t>-52,13; -21,18</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-7,47</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-6,61</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-6,87</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-4,97</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-3,34</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,89</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-7,47</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-6,61</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-5,53</t>
+          <t>-7,43</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,86</t>
+          <t>-7,16</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,05; -1,79</t>
+          <t>-11,07; -4,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 0,41</t>
+          <t>-9,96; -3,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 9,1</t>
+          <t>-10,3; -2,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,97; -3,99</t>
+          <t>-8,28; -1,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,93; -3,12</t>
+          <t>-7,23; 0,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,11; -1,07</t>
+          <t>-11,43; -3,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,75; -3,63</t>
+          <t>-8,88; -3,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,37; -2,57</t>
+          <t>-7,45; -2,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 1,3</t>
+          <t>-9,58; -4,18</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-31,9%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-28,24%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-29,33%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-19,64%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-13,19%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-7,45%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-31,9%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-28,24%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-23,61%</t>
+          <t>-29,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-15,87%</t>
+          <t>-29,42%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-32,4; -7,15</t>
+          <t>-43,41; -19,22</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-26,49; 1,72</t>
+          <t>-39,55; -15,81</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,22; 36,41</t>
+          <t>-41,16; -10,07</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,18; -18,03</t>
+          <t>-30,25; -4,38</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,49; -15,01</t>
+          <t>-26,46; 1,27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,26; -3,39</t>
+          <t>-41,52; -15,81</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-34,43; -16,05</t>
+          <t>-34,85; -16,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-29,05; -11,03</t>
+          <t>-29,16; -10,78</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 6,01</t>
+          <t>-37,77; -17,73</t>
         </is>
       </c>
     </row>
